--- a/Config/Datas/LevelDatas/LevelDatas.xlsx
+++ b/Config/Datas/LevelDatas/LevelDatas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\LevelDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B12D1123-7E29-4D0B-AE05-1A13D85AA503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55460643-010A-4F3C-A9A0-A7D6BED71A5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -56,6 +56,18 @@
   </si>
   <si>
     <t>一只全是猫猫的星球！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>灵屿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔肴森林</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M8星球</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -395,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -403,7 +415,7 @@
     <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -417,7 +429,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -431,7 +443,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B3" s="1">
         <v>1</v>
       </c>
@@ -440,6 +452,30 @@
       </c>
       <c r="D3" s="1" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B4" s="1">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B5" s="1">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B6" s="1">
+        <v>4</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
